--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1649"/>
+  <dimension ref="A1:H1654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35288,7 +35288,7 @@
       </c>
       <c r="F1605" t="inlineStr"/>
       <c r="G1605" t="n">
-        <v>70635006.21600001</v>
+        <v>70636594.21600001</v>
       </c>
       <c r="H1605" t="inlineStr"/>
     </row>
@@ -35310,7 +35310,7 @@
       </c>
       <c r="F1606" t="inlineStr"/>
       <c r="G1606" t="n">
-        <v>70299771.822</v>
+        <v>70299819.822</v>
       </c>
       <c r="H1606" t="inlineStr"/>
     </row>
@@ -35332,7 +35332,7 @@
       </c>
       <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="n">
-        <v>70587775.08499999</v>
+        <v>70587973.08499999</v>
       </c>
       <c r="H1607" t="inlineStr"/>
     </row>
@@ -35354,7 +35354,7 @@
       </c>
       <c r="F1608" t="inlineStr"/>
       <c r="G1608" t="n">
-        <v>70229580.022</v>
+        <v>70229881.022</v>
       </c>
       <c r="H1608" t="inlineStr"/>
     </row>
@@ -35376,7 +35376,7 @@
       </c>
       <c r="F1609" t="inlineStr"/>
       <c r="G1609" t="n">
-        <v>69901372.40099999</v>
+        <v>69901660.40099999</v>
       </c>
       <c r="H1609" t="inlineStr"/>
     </row>
@@ -35398,7 +35398,7 @@
       </c>
       <c r="F1610" t="inlineStr"/>
       <c r="G1610" t="n">
-        <v>69964158.51100001</v>
+        <v>69964490.51100001</v>
       </c>
       <c r="H1610" t="inlineStr"/>
     </row>
@@ -35420,7 +35420,7 @@
       </c>
       <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="n">
-        <v>67071887.542</v>
+        <v>67088752.542</v>
       </c>
       <c r="H1611" t="inlineStr"/>
     </row>
@@ -35442,7 +35442,7 @@
       </c>
       <c r="F1612" t="inlineStr"/>
       <c r="G1612" t="n">
-        <v>66241955.86</v>
+        <v>66242228.86</v>
       </c>
       <c r="H1612" t="inlineStr"/>
     </row>
@@ -35464,7 +35464,7 @@
       </c>
       <c r="F1613" t="inlineStr"/>
       <c r="G1613" t="n">
-        <v>65273840.505</v>
+        <v>65273842.505</v>
       </c>
       <c r="H1613" t="inlineStr"/>
     </row>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="F1614" t="inlineStr"/>
       <c r="G1614" t="n">
-        <v>65470550.935</v>
+        <v>65470563.935</v>
       </c>
       <c r="H1614" t="inlineStr"/>
     </row>
@@ -35508,7 +35508,7 @@
       </c>
       <c r="F1615" t="inlineStr"/>
       <c r="G1615" t="n">
-        <v>64013507.835</v>
+        <v>64013534.835</v>
       </c>
       <c r="H1615" t="inlineStr"/>
     </row>
@@ -35530,7 +35530,7 @@
       </c>
       <c r="F1616" t="inlineStr"/>
       <c r="G1616" t="n">
-        <v>64510440.378</v>
+        <v>64510542.378</v>
       </c>
       <c r="H1616" t="inlineStr"/>
     </row>
@@ -35552,7 +35552,7 @@
       </c>
       <c r="F1617" t="inlineStr"/>
       <c r="G1617" t="n">
-        <v>64115004.533</v>
+        <v>64115041.533</v>
       </c>
       <c r="H1617" t="inlineStr"/>
     </row>
@@ -35574,7 +35574,7 @@
       </c>
       <c r="F1618" t="inlineStr"/>
       <c r="G1618" t="n">
-        <v>63334802.238</v>
+        <v>63334869.238</v>
       </c>
       <c r="H1618" t="inlineStr"/>
     </row>
@@ -35596,7 +35596,7 @@
       </c>
       <c r="F1619" t="inlineStr"/>
       <c r="G1619" t="n">
-        <v>63707734.033</v>
+        <v>63707854.033</v>
       </c>
       <c r="H1619" t="inlineStr"/>
     </row>
@@ -35618,7 +35618,7 @@
       </c>
       <c r="F1620" t="inlineStr"/>
       <c r="G1620" t="n">
-        <v>63509636.358</v>
+        <v>63509715.358</v>
       </c>
       <c r="H1620" t="inlineStr"/>
     </row>
@@ -35640,7 +35640,7 @@
       </c>
       <c r="F1621" t="inlineStr"/>
       <c r="G1621" t="n">
-        <v>64246880.48</v>
+        <v>64247275.48</v>
       </c>
       <c r="H1621" t="inlineStr"/>
     </row>
@@ -35662,7 +35662,7 @@
       </c>
       <c r="F1622" t="inlineStr"/>
       <c r="G1622" t="n">
-        <v>63937633.388</v>
+        <v>63937689.388</v>
       </c>
       <c r="H1622" t="inlineStr"/>
     </row>
@@ -35684,7 +35684,7 @@
       </c>
       <c r="F1623" t="inlineStr"/>
       <c r="G1623" t="n">
-        <v>64760907.009</v>
+        <v>64760899.009</v>
       </c>
       <c r="H1623" t="inlineStr"/>
     </row>
@@ -35706,7 +35706,7 @@
       </c>
       <c r="F1624" t="inlineStr"/>
       <c r="G1624" t="n">
-        <v>66757474.503</v>
+        <v>66757481.503</v>
       </c>
       <c r="H1624" t="inlineStr"/>
     </row>
@@ -35730,7 +35730,7 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69577114.436</v>
+        <v>69590139.436</v>
       </c>
       <c r="H1625" t="n">
         <v>2.1</v>
@@ -35776,7 +35776,7 @@
       </c>
       <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="n">
-        <v>67719831.027</v>
+        <v>67719628.027</v>
       </c>
       <c r="H1627" t="inlineStr"/>
     </row>
@@ -35798,7 +35798,7 @@
       </c>
       <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="n">
-        <v>67970065.47499999</v>
+        <v>67969400.47499999</v>
       </c>
       <c r="H1628" t="inlineStr"/>
     </row>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="F1629" t="inlineStr"/>
       <c r="G1629" t="n">
-        <v>68795965.51199999</v>
+        <v>68797613.51199999</v>
       </c>
       <c r="H1629" t="inlineStr"/>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="n">
-        <v>66810936.598</v>
+        <v>66807792.598</v>
       </c>
       <c r="H1630" t="inlineStr"/>
     </row>
@@ -35864,7 +35864,7 @@
       </c>
       <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="n">
-        <v>65294237.905</v>
+        <v>65287024.905</v>
       </c>
       <c r="H1631" t="inlineStr"/>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="n">
-        <v>64479744.441</v>
+        <v>64475518.441</v>
       </c>
       <c r="H1632" t="inlineStr"/>
     </row>
@@ -35908,7 +35908,7 @@
       </c>
       <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="n">
-        <v>64617203.723</v>
+        <v>64615439.723</v>
       </c>
       <c r="H1633" t="inlineStr"/>
     </row>
@@ -35930,7 +35930,7 @@
       </c>
       <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="n">
-        <v>64848121.927</v>
+        <v>64845993.927</v>
       </c>
       <c r="H1634" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="n">
-        <v>64307567.931</v>
+        <v>64305439.931</v>
       </c>
       <c r="H1635" t="inlineStr"/>
     </row>
@@ -35974,7 +35974,7 @@
       </c>
       <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="n">
-        <v>63942170.667</v>
+        <v>63940043.667</v>
       </c>
       <c r="H1636" t="inlineStr"/>
     </row>
@@ -35996,7 +35996,7 @@
       </c>
       <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="n">
-        <v>63503581.828</v>
+        <v>63501453.828</v>
       </c>
       <c r="H1637" t="inlineStr"/>
     </row>
@@ -36018,7 +36018,7 @@
       </c>
       <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="n">
-        <v>62866644.53</v>
+        <v>62864516.53</v>
       </c>
       <c r="H1638" t="inlineStr"/>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="n">
-        <v>62663843.253</v>
+        <v>62661715.253</v>
       </c>
       <c r="H1639" t="inlineStr"/>
     </row>
@@ -36062,7 +36062,7 @@
       </c>
       <c r="F1640" t="inlineStr"/>
       <c r="G1640" t="n">
-        <v>62355511.352</v>
+        <v>62371214.352</v>
       </c>
       <c r="H1640" t="inlineStr"/>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="F1641" t="inlineStr"/>
       <c r="G1641" t="n">
-        <v>62677896.415</v>
+        <v>62691283.415</v>
       </c>
       <c r="H1641" t="inlineStr"/>
     </row>
@@ -36106,7 +36106,7 @@
       </c>
       <c r="F1642" t="inlineStr"/>
       <c r="G1642" t="n">
-        <v>63301175.944</v>
+        <v>63307728.092</v>
       </c>
       <c r="H1642" t="inlineStr"/>
     </row>
@@ -36128,7 +36128,7 @@
       </c>
       <c r="F1643" t="inlineStr"/>
       <c r="G1643" t="n">
-        <v>64002119.34</v>
+        <v>63987229.941</v>
       </c>
       <c r="H1643" t="inlineStr"/>
     </row>
@@ -36150,7 +36150,7 @@
       </c>
       <c r="F1644" t="inlineStr"/>
       <c r="G1644" t="n">
-        <v>65694753.122</v>
+        <v>65705530.541</v>
       </c>
       <c r="H1644" t="inlineStr"/>
     </row>
@@ -36174,9 +36174,11 @@
         <v>21</v>
       </c>
       <c r="G1645" t="n">
-        <v>68745902.84299999</v>
-      </c>
-      <c r="H1645" t="inlineStr"/>
+        <v>68593650.961</v>
+      </c>
+      <c r="H1645" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="1646">
       <c r="A1646" s="1" t="n">
@@ -36196,7 +36198,7 @@
       </c>
       <c r="F1646" t="inlineStr"/>
       <c r="G1646" t="n">
-        <v>67792457.311</v>
+        <v>67752854.09299999</v>
       </c>
       <c r="H1646" t="inlineStr"/>
     </row>
@@ -36217,15 +36219,21 @@
         <v>23.125</v>
       </c>
       <c r="F1647" t="inlineStr"/>
-      <c r="G1647" t="inlineStr"/>
+      <c r="G1647" t="n">
+        <v>67348227.30500001</v>
+      </c>
       <c r="H1647" t="inlineStr"/>
     </row>
     <row r="1648">
       <c r="A1648" s="1" t="n">
         <v>46268</v>
       </c>
-      <c r="B1648" t="inlineStr"/>
-      <c r="C1648" t="inlineStr"/>
+      <c r="B1648" t="n">
+        <v>50789</v>
+      </c>
+      <c r="C1648" t="n">
+        <v>47282027</v>
+      </c>
       <c r="D1648" t="n">
         <v>1529.42</v>
       </c>
@@ -36233,22 +36241,126 @@
         <v>23.25</v>
       </c>
       <c r="F1648" t="inlineStr"/>
-      <c r="G1648" t="inlineStr"/>
+      <c r="G1648" t="n">
+        <v>67728833.68799999</v>
+      </c>
       <c r="H1648" t="inlineStr"/>
     </row>
     <row r="1649">
       <c r="A1649" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B1649" t="inlineStr"/>
-      <c r="C1649" t="inlineStr"/>
+      <c r="B1649" t="n">
+        <v>50760</v>
+      </c>
+      <c r="C1649" t="n">
+        <v>47251329</v>
+      </c>
       <c r="D1649" t="n">
         <v>1528.6</v>
       </c>
-      <c r="E1649" t="inlineStr"/>
+      <c r="E1649" t="n">
+        <v>22.0625</v>
+      </c>
       <c r="F1649" t="inlineStr"/>
-      <c r="G1649" t="inlineStr"/>
+      <c r="G1649" t="n">
+        <v>67610127.728</v>
+      </c>
       <c r="H1649" t="inlineStr"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" s="1" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B1650" t="n">
+        <v>50738</v>
+      </c>
+      <c r="C1650" t="n">
+        <v>46768207</v>
+      </c>
+      <c r="D1650" t="n">
+        <v>1529.19</v>
+      </c>
+      <c r="E1650" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="F1650" t="inlineStr"/>
+      <c r="G1650" t="n">
+        <v>66230791.17</v>
+      </c>
+      <c r="H1650" t="inlineStr"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B1651" t="n">
+        <v>50732</v>
+      </c>
+      <c r="C1651" t="n">
+        <v>45504286</v>
+      </c>
+      <c r="D1651" t="n">
+        <v>1529.4</v>
+      </c>
+      <c r="E1651" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F1651" t="inlineStr"/>
+      <c r="G1651" t="n">
+        <v>65501817.069</v>
+      </c>
+      <c r="H1651" t="inlineStr"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B1652" t="n">
+        <v>50617</v>
+      </c>
+      <c r="C1652" t="n">
+        <v>45715105</v>
+      </c>
+      <c r="D1652" t="n">
+        <v>1533.53</v>
+      </c>
+      <c r="E1652" t="n">
+        <v>22.4375</v>
+      </c>
+      <c r="F1652" t="inlineStr"/>
+      <c r="G1652" t="inlineStr"/>
+      <c r="H1652" t="inlineStr"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" s="1" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B1653" t="inlineStr"/>
+      <c r="C1653" t="inlineStr"/>
+      <c r="D1653" t="n">
+        <v>1533.98</v>
+      </c>
+      <c r="E1653" t="n">
+        <v>22.3125</v>
+      </c>
+      <c r="F1653" t="inlineStr"/>
+      <c r="G1653" t="inlineStr"/>
+      <c r="H1653" t="inlineStr"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B1654" t="inlineStr"/>
+      <c r="C1654" t="inlineStr"/>
+      <c r="D1654" t="n">
+        <v>1531.73</v>
+      </c>
+      <c r="E1654" t="inlineStr"/>
+      <c r="F1654" t="inlineStr"/>
+      <c r="G1654" t="inlineStr"/>
+      <c r="H1654" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1654"/>
+  <dimension ref="A1:H1659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60377522.102</v>
+        <v>60377518.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -35730,7 +35730,7 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69590139.436</v>
+        <v>69618064.566</v>
       </c>
       <c r="H1625" t="n">
         <v>2.1</v>
@@ -36174,7 +36174,7 @@
         <v>21</v>
       </c>
       <c r="G1645" t="n">
-        <v>68593650.961</v>
+        <v>68593674.961</v>
       </c>
       <c r="H1645" t="n">
         <v>1.7</v>
@@ -36198,7 +36198,7 @@
       </c>
       <c r="F1646" t="inlineStr"/>
       <c r="G1646" t="n">
-        <v>67752854.09299999</v>
+        <v>67754582.09299999</v>
       </c>
       <c r="H1646" t="inlineStr"/>
     </row>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="F1647" t="inlineStr"/>
       <c r="G1647" t="n">
-        <v>67348227.30500001</v>
+        <v>67327953.691</v>
       </c>
       <c r="H1647" t="inlineStr"/>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="F1648" t="inlineStr"/>
       <c r="G1648" t="n">
-        <v>67728833.68799999</v>
+        <v>67684498.664</v>
       </c>
       <c r="H1648" t="inlineStr"/>
     </row>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="F1649" t="inlineStr"/>
       <c r="G1649" t="n">
-        <v>67610127.728</v>
+        <v>67581200.706</v>
       </c>
       <c r="H1649" t="inlineStr"/>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="F1650" t="inlineStr"/>
       <c r="G1650" t="n">
-        <v>66230791.17</v>
+        <v>66111284.901</v>
       </c>
       <c r="H1650" t="inlineStr"/>
     </row>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="n">
-        <v>65501817.069</v>
+        <v>65816812.019</v>
       </c>
       <c r="H1651" t="inlineStr"/>
     </row>
@@ -36329,15 +36329,21 @@
         <v>22.4375</v>
       </c>
       <c r="F1652" t="inlineStr"/>
-      <c r="G1652" t="inlineStr"/>
+      <c r="G1652" t="n">
+        <v>64894790.099</v>
+      </c>
       <c r="H1652" t="inlineStr"/>
     </row>
     <row r="1653">
       <c r="A1653" s="1" t="n">
         <v>46275</v>
       </c>
-      <c r="B1653" t="inlineStr"/>
-      <c r="C1653" t="inlineStr"/>
+      <c r="B1653" t="n">
+        <v>50506</v>
+      </c>
+      <c r="C1653" t="n">
+        <v>45765350</v>
+      </c>
       <c r="D1653" t="n">
         <v>1533.98</v>
       </c>
@@ -36345,22 +36351,126 @@
         <v>22.3125</v>
       </c>
       <c r="F1653" t="inlineStr"/>
-      <c r="G1653" t="inlineStr"/>
+      <c r="G1653" t="n">
+        <v>64542399.057</v>
+      </c>
       <c r="H1653" t="inlineStr"/>
     </row>
     <row r="1654">
       <c r="A1654" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="B1654" t="inlineStr"/>
-      <c r="C1654" t="inlineStr"/>
+      <c r="B1654" t="n">
+        <v>50474</v>
+      </c>
+      <c r="C1654" t="n">
+        <v>45878260</v>
+      </c>
       <c r="D1654" t="n">
         <v>1531.73</v>
       </c>
-      <c r="E1654" t="inlineStr"/>
+      <c r="E1654" t="n">
+        <v>21.4375</v>
+      </c>
       <c r="F1654" t="inlineStr"/>
-      <c r="G1654" t="inlineStr"/>
+      <c r="G1654" t="n">
+        <v>64915851.948</v>
+      </c>
       <c r="H1654" t="inlineStr"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1655" t="n">
+        <v>50404</v>
+      </c>
+      <c r="C1655" t="n">
+        <v>46909045</v>
+      </c>
+      <c r="D1655" t="n">
+        <v>1530.55</v>
+      </c>
+      <c r="E1655" t="n">
+        <v>22.125</v>
+      </c>
+      <c r="F1655" t="inlineStr"/>
+      <c r="G1655" t="n">
+        <v>64693370.279</v>
+      </c>
+      <c r="H1655" t="inlineStr"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1656" t="n">
+        <v>49954</v>
+      </c>
+      <c r="C1656" t="n">
+        <v>46310910</v>
+      </c>
+      <c r="D1656" t="n">
+        <v>1532.27</v>
+      </c>
+      <c r="E1656" t="n">
+        <v>22.5625</v>
+      </c>
+      <c r="F1656" t="inlineStr"/>
+      <c r="G1656" t="n">
+        <v>64672967.924</v>
+      </c>
+      <c r="H1656" t="inlineStr"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1657" t="n">
+        <v>50003</v>
+      </c>
+      <c r="C1657" t="n">
+        <v>45437976</v>
+      </c>
+      <c r="D1657" t="n">
+        <v>1531.56</v>
+      </c>
+      <c r="E1657" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="F1657" t="inlineStr"/>
+      <c r="G1657" t="inlineStr"/>
+      <c r="H1657" t="inlineStr"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1658" t="inlineStr"/>
+      <c r="C1658" t="inlineStr"/>
+      <c r="D1658" t="n">
+        <v>1531.98</v>
+      </c>
+      <c r="E1658" t="n">
+        <v>22.0625</v>
+      </c>
+      <c r="F1658" t="inlineStr"/>
+      <c r="G1658" t="inlineStr"/>
+      <c r="H1658" t="inlineStr"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1659" t="inlineStr"/>
+      <c r="C1659" t="inlineStr"/>
+      <c r="D1659" t="n">
+        <v>1534</v>
+      </c>
+      <c r="E1659" t="inlineStr"/>
+      <c r="F1659" t="inlineStr"/>
+      <c r="G1659" t="inlineStr"/>
+      <c r="H1659" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1659"/>
+  <dimension ref="A1:H1665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -32572,7 +32572,7 @@
       </c>
       <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="n">
-        <v>65326416.703</v>
+        <v>65326466.703</v>
       </c>
       <c r="H1481" t="inlineStr"/>
     </row>
@@ -33462,7 +33462,7 @@
       </c>
       <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="n">
-        <v>60377518.102</v>
+        <v>60377504.102</v>
       </c>
       <c r="H1522" t="inlineStr"/>
     </row>
@@ -35730,7 +35730,7 @@
         <v>21.8</v>
       </c>
       <c r="G1625" t="n">
-        <v>69618064.566</v>
+        <v>69618062.545</v>
       </c>
       <c r="H1625" t="n">
         <v>2.1</v>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="n">
-        <v>64305439.931</v>
+        <v>64312580.931</v>
       </c>
       <c r="H1635" t="inlineStr"/>
     </row>
@@ -35974,7 +35974,7 @@
       </c>
       <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="n">
-        <v>63940043.667</v>
+        <v>63942647.667</v>
       </c>
       <c r="H1636" t="inlineStr"/>
     </row>
@@ -35996,7 +35996,7 @@
       </c>
       <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="n">
-        <v>63501453.828</v>
+        <v>63504637.828</v>
       </c>
       <c r="H1637" t="inlineStr"/>
     </row>
@@ -36018,7 +36018,7 @@
       </c>
       <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="n">
-        <v>62864516.53</v>
+        <v>62866979.53</v>
       </c>
       <c r="H1638" t="inlineStr"/>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="n">
-        <v>62661715.253</v>
+        <v>62668146.253</v>
       </c>
       <c r="H1639" t="inlineStr"/>
     </row>
@@ -36174,7 +36174,7 @@
         <v>21</v>
       </c>
       <c r="G1645" t="n">
-        <v>68593674.961</v>
+        <v>68617235.78200001</v>
       </c>
       <c r="H1645" t="n">
         <v>1.7</v>
@@ -36198,7 +36198,7 @@
       </c>
       <c r="F1646" t="inlineStr"/>
       <c r="G1646" t="n">
-        <v>67754582.09299999</v>
+        <v>67750781.09299999</v>
       </c>
       <c r="H1646" t="inlineStr"/>
     </row>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="F1647" t="inlineStr"/>
       <c r="G1647" t="n">
-        <v>67327953.691</v>
+        <v>67323231.691</v>
       </c>
       <c r="H1647" t="inlineStr"/>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="F1648" t="inlineStr"/>
       <c r="G1648" t="n">
-        <v>67684498.664</v>
+        <v>67679772.664</v>
       </c>
       <c r="H1648" t="inlineStr"/>
     </row>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="F1649" t="inlineStr"/>
       <c r="G1649" t="n">
-        <v>67581200.706</v>
+        <v>67581404.706</v>
       </c>
       <c r="H1649" t="inlineStr"/>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="F1650" t="inlineStr"/>
       <c r="G1650" t="n">
-        <v>66111284.901</v>
+        <v>66112063.901</v>
       </c>
       <c r="H1650" t="inlineStr"/>
     </row>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="n">
-        <v>65816812.019</v>
+        <v>65264287.208</v>
       </c>
       <c r="H1651" t="inlineStr"/>
     </row>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="F1652" t="inlineStr"/>
       <c r="G1652" t="n">
-        <v>64894790.099</v>
+        <v>64696627.225</v>
       </c>
       <c r="H1652" t="inlineStr"/>
     </row>
@@ -36352,7 +36352,7 @@
       </c>
       <c r="F1653" t="inlineStr"/>
       <c r="G1653" t="n">
-        <v>64542399.057</v>
+        <v>64512069.884</v>
       </c>
       <c r="H1653" t="inlineStr"/>
     </row>
@@ -36374,7 +36374,7 @@
       </c>
       <c r="F1654" t="inlineStr"/>
       <c r="G1654" t="n">
-        <v>64915851.948</v>
+        <v>64769450.016</v>
       </c>
       <c r="H1654" t="inlineStr"/>
     </row>
@@ -36396,7 +36396,7 @@
       </c>
       <c r="F1655" t="inlineStr"/>
       <c r="G1655" t="n">
-        <v>64693370.279</v>
+        <v>64714783.464</v>
       </c>
       <c r="H1655" t="inlineStr"/>
     </row>
@@ -36418,7 +36418,7 @@
       </c>
       <c r="F1656" t="inlineStr"/>
       <c r="G1656" t="n">
-        <v>64672967.924</v>
+        <v>64466421.786</v>
       </c>
       <c r="H1656" t="inlineStr"/>
     </row>
@@ -36439,15 +36439,21 @@
         <v>22.75</v>
       </c>
       <c r="F1657" t="inlineStr"/>
-      <c r="G1657" t="inlineStr"/>
+      <c r="G1657" t="n">
+        <v>63466673.469</v>
+      </c>
       <c r="H1657" t="inlineStr"/>
     </row>
     <row r="1658">
       <c r="A1658" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1658" t="inlineStr"/>
-      <c r="C1658" t="inlineStr"/>
+      <c r="B1658" t="n">
+        <v>49786</v>
+      </c>
+      <c r="C1658" t="n">
+        <v>45951683</v>
+      </c>
       <c r="D1658" t="n">
         <v>1531.98</v>
       </c>
@@ -36455,22 +36461,148 @@
         <v>22.0625</v>
       </c>
       <c r="F1658" t="inlineStr"/>
-      <c r="G1658" t="inlineStr"/>
+      <c r="G1658" t="n">
+        <v>63653145.46</v>
+      </c>
       <c r="H1658" t="inlineStr"/>
     </row>
     <row r="1659">
       <c r="A1659" s="1" t="n">
         <v>46283</v>
       </c>
-      <c r="B1659" t="inlineStr"/>
-      <c r="C1659" t="inlineStr"/>
+      <c r="B1659" t="n">
+        <v>49803</v>
+      </c>
+      <c r="C1659" t="n">
+        <v>46162292</v>
+      </c>
       <c r="D1659" t="n">
         <v>1534</v>
       </c>
-      <c r="E1659" t="inlineStr"/>
+      <c r="E1659" t="n">
+        <v>22.0625</v>
+      </c>
       <c r="F1659" t="inlineStr"/>
-      <c r="G1659" t="inlineStr"/>
+      <c r="G1659" t="n">
+        <v>62970833.742</v>
+      </c>
       <c r="H1659" t="inlineStr"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1660" t="n">
+        <v>49696</v>
+      </c>
+      <c r="C1660" t="n">
+        <v>46275967</v>
+      </c>
+      <c r="D1660" t="n">
+        <v>1534.22</v>
+      </c>
+      <c r="E1660" t="n">
+        <v>22</v>
+      </c>
+      <c r="F1660" t="inlineStr"/>
+      <c r="G1660" t="n">
+        <v>62935637.588</v>
+      </c>
+      <c r="H1660" t="inlineStr"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1661" t="n">
+        <v>49412</v>
+      </c>
+      <c r="C1661" t="n">
+        <v>46551946</v>
+      </c>
+      <c r="D1661" t="n">
+        <v>1533.83</v>
+      </c>
+      <c r="E1661" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F1661" t="inlineStr"/>
+      <c r="G1661" t="n">
+        <v>63215334.425</v>
+      </c>
+      <c r="H1661" t="inlineStr"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1662" t="n">
+        <v>48928</v>
+      </c>
+      <c r="C1662" t="n">
+        <v>45786163</v>
+      </c>
+      <c r="D1662" t="n">
+        <v>1536.17</v>
+      </c>
+      <c r="E1662" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F1662" t="inlineStr"/>
+      <c r="G1662" t="n">
+        <v>62858507.771</v>
+      </c>
+      <c r="H1662" t="inlineStr"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1663" t="n">
+        <v>48845</v>
+      </c>
+      <c r="C1663" t="n">
+        <v>46058967</v>
+      </c>
+      <c r="D1663" t="n">
+        <v>1538.39</v>
+      </c>
+      <c r="E1663" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1663" t="inlineStr"/>
+      <c r="G1663" t="inlineStr"/>
+      <c r="H1663" t="inlineStr"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1664" t="inlineStr"/>
+      <c r="C1664" t="inlineStr"/>
+      <c r="D1664" t="n">
+        <v>1545.12</v>
+      </c>
+      <c r="E1664" t="n">
+        <v>21.9375</v>
+      </c>
+      <c r="F1664" t="inlineStr"/>
+      <c r="G1664" t="inlineStr"/>
+      <c r="H1664" t="inlineStr"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1665" t="inlineStr"/>
+      <c r="C1665" t="inlineStr"/>
+      <c r="D1665" t="n">
+        <v>1550.12</v>
+      </c>
+      <c r="E1665" t="inlineStr"/>
+      <c r="F1665" t="inlineStr"/>
+      <c r="G1665" t="inlineStr"/>
+      <c r="H1665" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1665"/>
+  <dimension ref="A1:H1670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.29</v>
+        <v>108.48</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.48</v>
+        <v>108.61</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.61</v>
+        <v>108.63</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.63</v>
+        <v>108.72</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.72</v>
+        <v>108.86</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.86</v>
+        <v>108.96</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.96</v>
+        <v>108.97</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>108.97</v>
+        <v>109.05</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.05</v>
+        <v>109.11</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.11</v>
+        <v>109.21</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.21</v>
+        <v>109.46</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.46</v>
+        <v>109.64</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.64</v>
+        <v>109.67</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.67</v>
+        <v>109.71</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.71</v>
+        <v>109.79</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>109.79</v>
+        <v>110.08</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.08</v>
+        <v>110.11</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.11</v>
+        <v>110.15</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.15</v>
+        <v>110.5</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.5</v>
+        <v>110.68</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.68</v>
+        <v>110.71</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.71</v>
+        <v>110.75</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.75</v>
+        <v>110.92</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>110.92</v>
+        <v>111.37</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.37</v>
+        <v>111.46</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.46</v>
+        <v>111.49</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.49</v>
+        <v>111.52</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.52</v>
+        <v>111.59</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.59</v>
+        <v>111.67</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>111.67</v>
+        <v>112.01</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.01</v>
+        <v>112.17</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.17</v>
+        <v>112.21</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.21</v>
+        <v>112.24</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.24</v>
+        <v>112.48</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.48</v>
+        <v>112.71</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.71</v>
+        <v>112.8</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.8</v>
+        <v>112.83</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.83</v>
+        <v>112.89</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.89</v>
+        <v>112.95</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -29406,7 +29406,7 @@
       </c>
       <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="n">
-        <v>51107673.335</v>
+        <v>51103769.335</v>
       </c>
       <c r="H1337" t="inlineStr"/>
     </row>
@@ -29842,7 +29842,7 @@
         <v>20.8</v>
       </c>
       <c r="G1357" t="n">
-        <v>57851174.056</v>
+        <v>57850119.056</v>
       </c>
       <c r="H1357" t="n">
         <v>1.6</v>
@@ -36174,7 +36174,7 @@
         <v>21</v>
       </c>
       <c r="G1645" t="n">
-        <v>68617235.78200001</v>
+        <v>68658535.774</v>
       </c>
       <c r="H1645" t="n">
         <v>1.7</v>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="n">
-        <v>65264287.208</v>
+        <v>65265354.208</v>
       </c>
       <c r="H1651" t="inlineStr"/>
     </row>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="F1652" t="inlineStr"/>
       <c r="G1652" t="n">
-        <v>64696627.225</v>
+        <v>64697072.225</v>
       </c>
       <c r="H1652" t="inlineStr"/>
     </row>
@@ -36352,7 +36352,7 @@
       </c>
       <c r="F1653" t="inlineStr"/>
       <c r="G1653" t="n">
-        <v>64512069.884</v>
+        <v>64510091.884</v>
       </c>
       <c r="H1653" t="inlineStr"/>
     </row>
@@ -36374,7 +36374,7 @@
       </c>
       <c r="F1654" t="inlineStr"/>
       <c r="G1654" t="n">
-        <v>64769450.016</v>
+        <v>64774159.016</v>
       </c>
       <c r="H1654" t="inlineStr"/>
     </row>
@@ -36396,7 +36396,7 @@
       </c>
       <c r="F1655" t="inlineStr"/>
       <c r="G1655" t="n">
-        <v>64714783.464</v>
+        <v>64719062.464</v>
       </c>
       <c r="H1655" t="inlineStr"/>
     </row>
@@ -36418,7 +36418,7 @@
       </c>
       <c r="F1656" t="inlineStr"/>
       <c r="G1656" t="n">
-        <v>64466421.786</v>
+        <v>64470699.786</v>
       </c>
       <c r="H1656" t="inlineStr"/>
     </row>
@@ -36440,7 +36440,7 @@
       </c>
       <c r="F1657" t="inlineStr"/>
       <c r="G1657" t="n">
-        <v>63466673.469</v>
+        <v>63464202.469</v>
       </c>
       <c r="H1657" t="inlineStr"/>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="F1658" t="inlineStr"/>
       <c r="G1658" t="n">
-        <v>63653145.46</v>
+        <v>63556440.978</v>
       </c>
       <c r="H1658" t="inlineStr"/>
     </row>
@@ -36484,7 +36484,7 @@
       </c>
       <c r="F1659" t="inlineStr"/>
       <c r="G1659" t="n">
-        <v>62970833.742</v>
+        <v>62975162.742</v>
       </c>
       <c r="H1659" t="inlineStr"/>
     </row>
@@ -36506,7 +36506,7 @@
       </c>
       <c r="F1660" t="inlineStr"/>
       <c r="G1660" t="n">
-        <v>62935637.588</v>
+        <v>62788519.346</v>
       </c>
       <c r="H1660" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="F1661" t="inlineStr"/>
       <c r="G1661" t="n">
-        <v>63215334.425</v>
+        <v>62692173.519</v>
       </c>
       <c r="H1661" t="inlineStr"/>
     </row>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="F1662" t="inlineStr"/>
       <c r="G1662" t="n">
-        <v>62858507.771</v>
+        <v>62712236.715</v>
       </c>
       <c r="H1662" t="inlineStr"/>
     </row>
@@ -36571,15 +36571,21 @@
         <v>23</v>
       </c>
       <c r="F1663" t="inlineStr"/>
-      <c r="G1663" t="inlineStr"/>
+      <c r="G1663" t="n">
+        <v>63157419.297</v>
+      </c>
       <c r="H1663" t="inlineStr"/>
     </row>
     <row r="1664">
       <c r="A1664" s="1" t="n">
         <v>46290</v>
       </c>
-      <c r="B1664" t="inlineStr"/>
-      <c r="C1664" t="inlineStr"/>
+      <c r="B1664" t="n">
+        <v>48255</v>
+      </c>
+      <c r="C1664" t="n">
+        <v>45747929</v>
+      </c>
       <c r="D1664" t="n">
         <v>1545.12</v>
       </c>
@@ -36587,22 +36593,126 @@
         <v>21.9375</v>
       </c>
       <c r="F1664" t="inlineStr"/>
-      <c r="G1664" t="inlineStr"/>
+      <c r="G1664" t="n">
+        <v>63336872.687</v>
+      </c>
       <c r="H1664" t="inlineStr"/>
     </row>
     <row r="1665">
       <c r="A1665" s="1" t="n">
         <v>46293</v>
       </c>
-      <c r="B1665" t="inlineStr"/>
-      <c r="C1665" t="inlineStr"/>
+      <c r="B1665" t="n">
+        <v>47960</v>
+      </c>
+      <c r="C1665" t="n">
+        <v>46033138</v>
+      </c>
       <c r="D1665" t="n">
         <v>1550.12</v>
       </c>
-      <c r="E1665" t="inlineStr"/>
+      <c r="E1665" t="n">
+        <v>22.0625</v>
+      </c>
       <c r="F1665" t="inlineStr"/>
-      <c r="G1665" t="inlineStr"/>
+      <c r="G1665" t="n">
+        <v>64393525.521</v>
+      </c>
       <c r="H1665" t="inlineStr"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1666" t="n">
+        <v>47482</v>
+      </c>
+      <c r="C1666" t="n">
+        <v>46262060</v>
+      </c>
+      <c r="D1666" t="n">
+        <v>1543.93</v>
+      </c>
+      <c r="E1666" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="F1666" t="inlineStr"/>
+      <c r="G1666" t="n">
+        <v>65558563.646</v>
+      </c>
+      <c r="H1666" t="inlineStr"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1667" t="n">
+        <v>46092</v>
+      </c>
+      <c r="C1667" t="n">
+        <v>46909419</v>
+      </c>
+      <c r="D1667" t="n">
+        <v>1539.87</v>
+      </c>
+      <c r="E1667" t="n">
+        <v>22.8125</v>
+      </c>
+      <c r="F1667" t="inlineStr"/>
+      <c r="G1667" t="n">
+        <v>68875481.65800001</v>
+      </c>
+      <c r="H1667" t="inlineStr"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1668" t="n">
+        <v>48288</v>
+      </c>
+      <c r="C1668" t="n">
+        <v>46654181</v>
+      </c>
+      <c r="D1668" t="n">
+        <v>1543.96</v>
+      </c>
+      <c r="E1668" t="n">
+        <v>23.1875</v>
+      </c>
+      <c r="F1668" t="inlineStr"/>
+      <c r="G1668" t="inlineStr"/>
+      <c r="H1668" t="inlineStr"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1669" t="inlineStr"/>
+      <c r="C1669" t="inlineStr"/>
+      <c r="D1669" t="n">
+        <v>1543.18</v>
+      </c>
+      <c r="E1669" t="n">
+        <v>22.625</v>
+      </c>
+      <c r="F1669" t="inlineStr"/>
+      <c r="G1669" t="inlineStr"/>
+      <c r="H1669" t="inlineStr"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1670" t="inlineStr"/>
+      <c r="C1670" t="inlineStr"/>
+      <c r="D1670" t="n">
+        <v>1540.24</v>
+      </c>
+      <c r="E1670" t="inlineStr"/>
+      <c r="F1670" t="inlineStr"/>
+      <c r="G1670" t="inlineStr"/>
+      <c r="H1670" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/seriesAPI_BCRA_Digest.xlsx
+++ b/seriesAPI_BCRA_Digest.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1670"/>
+  <dimension ref="A1:H1674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10857,7 +10857,7 @@
         <v>3922697</v>
       </c>
       <c r="D496" t="n">
-        <v>108.48</v>
+        <v>108.29</v>
       </c>
       <c r="E496" t="n">
         <v>34.1875</v>
@@ -10879,7 +10879,7 @@
         <v>3851298</v>
       </c>
       <c r="D497" t="n">
-        <v>108.61</v>
+        <v>108.48</v>
       </c>
       <c r="E497" t="n">
         <v>34.25</v>
@@ -10901,7 +10901,7 @@
         <v>3950424</v>
       </c>
       <c r="D498" t="n">
-        <v>108.63</v>
+        <v>108.61</v>
       </c>
       <c r="E498" t="n">
         <v>34.25</v>
@@ -10923,7 +10923,7 @@
         <v>4326335</v>
       </c>
       <c r="D499" t="n">
-        <v>108.72</v>
+        <v>108.63</v>
       </c>
       <c r="E499" t="n">
         <v>34.1875</v>
@@ -10945,7 +10945,7 @@
         <v>3761928</v>
       </c>
       <c r="D500" t="n">
-        <v>108.86</v>
+        <v>108.72</v>
       </c>
       <c r="E500" t="n">
         <v>37.375</v>
@@ -10967,7 +10967,7 @@
         <v>3780254</v>
       </c>
       <c r="D501" t="n">
-        <v>108.96</v>
+        <v>108.86</v>
       </c>
       <c r="E501" t="n">
         <v>37.625</v>
@@ -10989,7 +10989,7 @@
         <v>3569643</v>
       </c>
       <c r="D502" t="n">
-        <v>108.97</v>
+        <v>108.96</v>
       </c>
       <c r="E502" t="n">
         <v>37.375</v>
@@ -11011,7 +11011,7 @@
         <v>3602002</v>
       </c>
       <c r="D503" t="n">
-        <v>109.05</v>
+        <v>108.97</v>
       </c>
       <c r="E503" t="n">
         <v>37.4375</v>
@@ -11033,7 +11033,7 @@
         <v>3521623</v>
       </c>
       <c r="D504" t="n">
-        <v>109.11</v>
+        <v>109.05</v>
       </c>
       <c r="E504" t="n">
         <v>37.4375</v>
@@ -11055,7 +11055,7 @@
         <v>3644760</v>
       </c>
       <c r="D505" t="n">
-        <v>109.21</v>
+        <v>109.11</v>
       </c>
       <c r="E505" t="n">
         <v>37.625</v>
@@ -11077,7 +11077,7 @@
         <v>3772372</v>
       </c>
       <c r="D506" t="n">
-        <v>109.46</v>
+        <v>109.21</v>
       </c>
       <c r="E506" t="n">
         <v>37.75</v>
@@ -11099,7 +11099,7 @@
         <v>3602872</v>
       </c>
       <c r="D507" t="n">
-        <v>109.64</v>
+        <v>109.46</v>
       </c>
       <c r="E507" t="n">
         <v>37.5</v>
@@ -11121,7 +11121,7 @@
         <v>3588642</v>
       </c>
       <c r="D508" t="n">
-        <v>109.67</v>
+        <v>109.64</v>
       </c>
       <c r="E508" t="n">
         <v>37.5625</v>
@@ -11143,7 +11143,7 @@
         <v>3546894</v>
       </c>
       <c r="D509" t="n">
-        <v>109.71</v>
+        <v>109.67</v>
       </c>
       <c r="E509" t="n">
         <v>37.625</v>
@@ -11165,7 +11165,7 @@
         <v>3547947</v>
       </c>
       <c r="D510" t="n">
-        <v>109.79</v>
+        <v>109.71</v>
       </c>
       <c r="E510" t="n">
         <v>37.5</v>
@@ -11187,7 +11187,7 @@
         <v>3659413</v>
       </c>
       <c r="D511" t="n">
-        <v>110.08</v>
+        <v>109.79</v>
       </c>
       <c r="E511" t="n">
         <v>37.625</v>
@@ -11209,7 +11209,7 @@
         <v>3609733</v>
       </c>
       <c r="D512" t="n">
-        <v>110.11</v>
+        <v>110.08</v>
       </c>
       <c r="E512" t="n">
         <v>37.625</v>
@@ -11231,7 +11231,7 @@
         <v>3620102</v>
       </c>
       <c r="D513" t="n">
-        <v>110.15</v>
+        <v>110.11</v>
       </c>
       <c r="E513" t="n">
         <v>37.5625</v>
@@ -11253,7 +11253,7 @@
         <v>3597892</v>
       </c>
       <c r="D514" t="n">
-        <v>110.5</v>
+        <v>110.15</v>
       </c>
       <c r="E514" t="n">
         <v>37.5625</v>
@@ -11275,7 +11275,7 @@
         <v>3643133</v>
       </c>
       <c r="D515" t="n">
-        <v>110.68</v>
+        <v>110.5</v>
       </c>
       <c r="E515" t="n">
         <v>37.75</v>
@@ -11297,7 +11297,7 @@
         <v>3631047</v>
       </c>
       <c r="D516" t="n">
-        <v>110.71</v>
+        <v>110.68</v>
       </c>
       <c r="E516" t="n">
         <v>37.625</v>
@@ -11323,7 +11323,7 @@
         <v>3880988</v>
       </c>
       <c r="D517" t="n">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="E517" t="n">
         <v>37.5</v>
@@ -11345,7 +11345,7 @@
         <v>3857121</v>
       </c>
       <c r="D518" t="n">
-        <v>110.92</v>
+        <v>110.75</v>
       </c>
       <c r="E518" t="n">
         <v>37.5625</v>
@@ -11389,7 +11389,7 @@
         <v>3705419</v>
       </c>
       <c r="D520" t="n">
-        <v>111.37</v>
+        <v>110.92</v>
       </c>
       <c r="E520" t="n">
         <v>37.5625</v>
@@ -11411,7 +11411,7 @@
         <v>3631309</v>
       </c>
       <c r="D521" t="n">
-        <v>111.46</v>
+        <v>111.37</v>
       </c>
       <c r="E521" t="n">
         <v>37.375</v>
@@ -11433,7 +11433,7 @@
         <v>3750052</v>
       </c>
       <c r="D522" t="n">
-        <v>111.49</v>
+        <v>111.46</v>
       </c>
       <c r="E522" t="n">
         <v>37.4375</v>
@@ -11455,7 +11455,7 @@
         <v>3709414</v>
       </c>
       <c r="D523" t="n">
-        <v>111.52</v>
+        <v>111.49</v>
       </c>
       <c r="E523" t="n">
         <v>37.6875</v>
@@ -11477,7 +11477,7 @@
         <v>3745962</v>
       </c>
       <c r="D524" t="n">
-        <v>111.59</v>
+        <v>111.52</v>
       </c>
       <c r="E524" t="n">
         <v>37.5</v>
@@ -11499,7 +11499,7 @@
         <v>3784898</v>
       </c>
       <c r="D525" t="n">
-        <v>111.67</v>
+        <v>111.59</v>
       </c>
       <c r="E525" t="n">
         <v>37.5625</v>
@@ -11521,7 +11521,7 @@
         <v>3926458</v>
       </c>
       <c r="D526" t="n">
-        <v>112.01</v>
+        <v>111.67</v>
       </c>
       <c r="E526" t="n">
         <v>37.5</v>
@@ -11543,7 +11543,7 @@
         <v>3994573</v>
       </c>
       <c r="D527" t="n">
-        <v>112.17</v>
+        <v>112.01</v>
       </c>
       <c r="E527" t="n">
         <v>37.625</v>
@@ -11565,7 +11565,7 @@
         <v>3906529</v>
       </c>
       <c r="D528" t="n">
-        <v>112.21</v>
+        <v>112.17</v>
       </c>
       <c r="E528" t="n">
         <v>37.6875</v>
@@ -11587,7 +11587,7 @@
         <v>3821174</v>
       </c>
       <c r="D529" t="n">
-        <v>112.24</v>
+        <v>112.21</v>
       </c>
       <c r="E529" t="n">
         <v>37.625</v>
@@ -11609,7 +11609,7 @@
         <v>3729418</v>
       </c>
       <c r="D530" t="n">
-        <v>112.48</v>
+        <v>112.24</v>
       </c>
       <c r="E530" t="n">
         <v>39.9375</v>
@@ -11631,7 +11631,7 @@
         <v>3812115</v>
       </c>
       <c r="D531" t="n">
-        <v>112.71</v>
+        <v>112.48</v>
       </c>
       <c r="E531" t="n">
         <v>39.875</v>
@@ -11653,7 +11653,7 @@
         <v>3644962</v>
       </c>
       <c r="D532" t="n">
-        <v>112.8</v>
+        <v>112.71</v>
       </c>
       <c r="E532" t="n">
         <v>40.0625</v>
@@ -11675,7 +11675,7 @@
         <v>3592761</v>
       </c>
       <c r="D533" t="n">
-        <v>112.83</v>
+        <v>112.8</v>
       </c>
       <c r="E533" t="n">
         <v>40.0625</v>
@@ -11697,7 +11697,7 @@
         <v>3676507</v>
       </c>
       <c r="D534" t="n">
-        <v>112.89</v>
+        <v>112.83</v>
       </c>
       <c r="E534" t="n">
         <v>39.9375</v>
@@ -11719,7 +11719,7 @@
         <v>3672002</v>
       </c>
       <c r="D535" t="n">
-        <v>112.95</v>
+        <v>112.89</v>
       </c>
       <c r="E535" t="n">
         <v>39.9375</v>
@@ -32138,7 +32138,7 @@
       </c>
       <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="n">
-        <v>56142524.43</v>
+        <v>56139608.43</v>
       </c>
       <c r="H1461" t="inlineStr"/>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="n">
-        <v>61217732.519</v>
+        <v>61248730.519</v>
       </c>
       <c r="H1485" t="inlineStr"/>
     </row>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="n">
-        <v>55098027.613</v>
+        <v>55044709.613</v>
       </c>
       <c r="H1497" t="inlineStr"/>
     </row>
@@ -33132,7 +33132,7 @@
       </c>
       <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="n">
-        <v>58642328.727</v>
+        <v>58628417.727</v>
       </c>
       <c r="H1507" t="inlineStr"/>
     </row>
@@ -35754,7 +35754,7 @@
       </c>
       <c r="F1626" t="inlineStr"/>
       <c r="G1626" t="n">
-        <v>68153020.20999999</v>
+        <v>68153184.20999999</v>
       </c>
       <c r="H1626" t="inlineStr"/>
     </row>
@@ -35776,7 +35776,7 @@
       </c>
       <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="n">
-        <v>67719628.027</v>
+        <v>67719794.027</v>
       </c>
       <c r="H1627" t="inlineStr"/>
     </row>
@@ -35798,7 +35798,7 @@
       </c>
       <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="n">
-        <v>67969400.47499999</v>
+        <v>67969556.47499999</v>
       </c>
       <c r="H1628" t="inlineStr"/>
     </row>
@@ -35820,7 +35820,7 @@
       </c>
       <c r="F1629" t="inlineStr"/>
       <c r="G1629" t="n">
-        <v>68797613.51199999</v>
+        <v>68798730.51199999</v>
       </c>
       <c r="H1629" t="inlineStr"/>
     </row>
@@ -35842,7 +35842,7 @@
       </c>
       <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="n">
-        <v>66807792.598</v>
+        <v>66807994.598</v>
       </c>
       <c r="H1630" t="inlineStr"/>
     </row>
@@ -35864,7 +35864,7 @@
       </c>
       <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="n">
-        <v>65287024.905</v>
+        <v>65287187.905</v>
       </c>
       <c r="H1631" t="inlineStr"/>
     </row>
@@ -35886,7 +35886,7 @@
       </c>
       <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="n">
-        <v>64475518.441</v>
+        <v>64475530.441</v>
       </c>
       <c r="H1632" t="inlineStr"/>
     </row>
@@ -35908,7 +35908,7 @@
       </c>
       <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="n">
-        <v>64615439.723</v>
+        <v>64615476.723</v>
       </c>
       <c r="H1633" t="inlineStr"/>
     </row>
@@ -35930,7 +35930,7 @@
       </c>
       <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="n">
-        <v>64845993.927</v>
+        <v>64846040.927</v>
       </c>
       <c r="H1634" t="inlineStr"/>
     </row>
@@ -35952,7 +35952,7 @@
       </c>
       <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="n">
-        <v>64312580.931</v>
+        <v>64312647.931</v>
       </c>
       <c r="H1635" t="inlineStr"/>
     </row>
@@ -35974,7 +35974,7 @@
       </c>
       <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="n">
-        <v>63942647.667</v>
+        <v>63942731.667</v>
       </c>
       <c r="H1636" t="inlineStr"/>
     </row>
@@ -35996,7 +35996,7 @@
       </c>
       <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="n">
-        <v>63504637.828</v>
+        <v>63504755.828</v>
       </c>
       <c r="H1637" t="inlineStr"/>
     </row>
@@ -36018,7 +36018,7 @@
       </c>
       <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="n">
-        <v>62866979.53</v>
+        <v>62867066.53</v>
       </c>
       <c r="H1638" t="inlineStr"/>
     </row>
@@ -36040,7 +36040,7 @@
       </c>
       <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="n">
-        <v>62668146.253</v>
+        <v>62668215.253</v>
       </c>
       <c r="H1639" t="inlineStr"/>
     </row>
@@ -36062,7 +36062,7 @@
       </c>
       <c r="F1640" t="inlineStr"/>
       <c r="G1640" t="n">
-        <v>62371214.352</v>
+        <v>62371239.352</v>
       </c>
       <c r="H1640" t="inlineStr"/>
     </row>
@@ -36084,7 +36084,7 @@
       </c>
       <c r="F1641" t="inlineStr"/>
       <c r="G1641" t="n">
-        <v>62691283.415</v>
+        <v>62691301.415</v>
       </c>
       <c r="H1641" t="inlineStr"/>
     </row>
@@ -36106,7 +36106,7 @@
       </c>
       <c r="F1642" t="inlineStr"/>
       <c r="G1642" t="n">
-        <v>63307728.092</v>
+        <v>63307729.092</v>
       </c>
       <c r="H1642" t="inlineStr"/>
     </row>
@@ -36128,7 +36128,7 @@
       </c>
       <c r="F1643" t="inlineStr"/>
       <c r="G1643" t="n">
-        <v>63987229.941</v>
+        <v>63987224.941</v>
       </c>
       <c r="H1643" t="inlineStr"/>
     </row>
@@ -36150,7 +36150,7 @@
       </c>
       <c r="F1644" t="inlineStr"/>
       <c r="G1644" t="n">
-        <v>65705530.541</v>
+        <v>65705509.541</v>
       </c>
       <c r="H1644" t="inlineStr"/>
     </row>
@@ -36174,7 +36174,7 @@
         <v>21</v>
       </c>
       <c r="G1645" t="n">
-        <v>68658535.774</v>
+        <v>68649515.774</v>
       </c>
       <c r="H1645" t="n">
         <v>1.7</v>
@@ -36198,7 +36198,7 @@
       </c>
       <c r="F1646" t="inlineStr"/>
       <c r="G1646" t="n">
-        <v>67750781.09299999</v>
+        <v>67750731.09299999</v>
       </c>
       <c r="H1646" t="inlineStr"/>
     </row>
@@ -36220,7 +36220,7 @@
       </c>
       <c r="F1647" t="inlineStr"/>
       <c r="G1647" t="n">
-        <v>67323231.691</v>
+        <v>67283667.691</v>
       </c>
       <c r="H1647" t="inlineStr"/>
     </row>
@@ -36242,7 +36242,7 @@
       </c>
       <c r="F1648" t="inlineStr"/>
       <c r="G1648" t="n">
-        <v>67679772.664</v>
+        <v>67679723.664</v>
       </c>
       <c r="H1648" t="inlineStr"/>
     </row>
@@ -36264,7 +36264,7 @@
       </c>
       <c r="F1649" t="inlineStr"/>
       <c r="G1649" t="n">
-        <v>67581404.706</v>
+        <v>67581355.706</v>
       </c>
       <c r="H1649" t="inlineStr"/>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="F1650" t="inlineStr"/>
       <c r="G1650" t="n">
-        <v>66112063.901</v>
+        <v>66112013.901</v>
       </c>
       <c r="H1650" t="inlineStr"/>
     </row>
@@ -36308,7 +36308,7 @@
       </c>
       <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="n">
-        <v>65265354.208</v>
+        <v>65265305.208</v>
       </c>
       <c r="H1651" t="inlineStr"/>
     </row>
@@ -36330,7 +36330,7 @@
       </c>
       <c r="F1652" t="inlineStr"/>
       <c r="G1652" t="n">
-        <v>64697072.225</v>
+        <v>64697023.225</v>
       </c>
       <c r="H1652" t="inlineStr"/>
     </row>
@@ -36352,7 +36352,7 @@
       </c>
       <c r="F1653" t="inlineStr"/>
       <c r="G1653" t="n">
-        <v>64510091.884</v>
+        <v>64510042.884</v>
       </c>
       <c r="H1653" t="inlineStr"/>
     </row>
@@ -36374,7 +36374,7 @@
       </c>
       <c r="F1654" t="inlineStr"/>
       <c r="G1654" t="n">
-        <v>64774159.016</v>
+        <v>64774109.016</v>
       </c>
       <c r="H1654" t="inlineStr"/>
     </row>
@@ -36396,7 +36396,7 @@
       </c>
       <c r="F1655" t="inlineStr"/>
       <c r="G1655" t="n">
-        <v>64719062.464</v>
+        <v>64719013.464</v>
       </c>
       <c r="H1655" t="inlineStr"/>
     </row>
@@ -36418,7 +36418,7 @@
       </c>
       <c r="F1656" t="inlineStr"/>
       <c r="G1656" t="n">
-        <v>64470699.786</v>
+        <v>64470650.786</v>
       </c>
       <c r="H1656" t="inlineStr"/>
     </row>
@@ -36440,7 +36440,7 @@
       </c>
       <c r="F1657" t="inlineStr"/>
       <c r="G1657" t="n">
-        <v>63464202.469</v>
+        <v>63464152.469</v>
       </c>
       <c r="H1657" t="inlineStr"/>
     </row>
@@ -36462,7 +36462,7 @@
       </c>
       <c r="F1658" t="inlineStr"/>
       <c r="G1658" t="n">
-        <v>63556440.978</v>
+        <v>63556390.978</v>
       </c>
       <c r="H1658" t="inlineStr"/>
     </row>
@@ -36484,7 +36484,7 @@
       </c>
       <c r="F1659" t="inlineStr"/>
       <c r="G1659" t="n">
-        <v>62975162.742</v>
+        <v>62974433.742</v>
       </c>
       <c r="H1659" t="inlineStr"/>
     </row>
@@ -36506,7 +36506,7 @@
       </c>
       <c r="F1660" t="inlineStr"/>
       <c r="G1660" t="n">
-        <v>62788519.346</v>
+        <v>62781441.346</v>
       </c>
       <c r="H1660" t="inlineStr"/>
     </row>
@@ -36528,7 +36528,7 @@
       </c>
       <c r="F1661" t="inlineStr"/>
       <c r="G1661" t="n">
-        <v>62692173.519</v>
+        <v>62692123.519</v>
       </c>
       <c r="H1661" t="inlineStr"/>
     </row>
@@ -36550,7 +36550,7 @@
       </c>
       <c r="F1662" t="inlineStr"/>
       <c r="G1662" t="n">
-        <v>62712236.715</v>
+        <v>62707710.715</v>
       </c>
       <c r="H1662" t="inlineStr"/>
     </row>
@@ -36572,7 +36572,7 @@
       </c>
       <c r="F1663" t="inlineStr"/>
       <c r="G1663" t="n">
-        <v>63157419.297</v>
+        <v>63154365.63</v>
       </c>
       <c r="H1663" t="inlineStr"/>
     </row>
@@ -36594,7 +36594,7 @@
       </c>
       <c r="F1664" t="inlineStr"/>
       <c r="G1664" t="n">
-        <v>63336872.687</v>
+        <v>63380126.328</v>
       </c>
       <c r="H1664" t="inlineStr"/>
     </row>
@@ -36616,7 +36616,7 @@
       </c>
       <c r="F1665" t="inlineStr"/>
       <c r="G1665" t="n">
-        <v>64393525.521</v>
+        <v>64398746.34</v>
       </c>
       <c r="H1665" t="inlineStr"/>
     </row>
@@ -36638,7 +36638,7 @@
       </c>
       <c r="F1666" t="inlineStr"/>
       <c r="G1666" t="n">
-        <v>65558563.646</v>
+        <v>65581501.771</v>
       </c>
       <c r="H1666" t="inlineStr"/>
     </row>
@@ -36658,9 +36658,11 @@
       <c r="E1667" t="n">
         <v>22.8125</v>
       </c>
-      <c r="F1667" t="inlineStr"/>
+      <c r="F1667" t="n">
+        <v>21.1</v>
+      </c>
       <c r="G1667" t="n">
-        <v>68875481.65800001</v>
+        <v>69007728.62899999</v>
       </c>
       <c r="H1667" t="inlineStr"/>
     </row>
@@ -36681,15 +36683,21 @@
         <v>23.1875</v>
       </c>
       <c r="F1668" t="inlineStr"/>
-      <c r="G1668" t="inlineStr"/>
+      <c r="G1668" t="n">
+        <v>69444779.214</v>
+      </c>
       <c r="H1668" t="inlineStr"/>
     </row>
     <row r="1669">
       <c r="A1669" s="1" t="n">
         <v>46297</v>
       </c>
-      <c r="B1669" t="inlineStr"/>
-      <c r="C1669" t="inlineStr"/>
+      <c r="B1669" t="n">
+        <v>48657</v>
+      </c>
+      <c r="C1669" t="n">
+        <v>46002173</v>
+      </c>
       <c r="D1669" t="n">
         <v>1543.18</v>
       </c>
@@ -36697,22 +36705,104 @@
         <v>22.625</v>
       </c>
       <c r="F1669" t="inlineStr"/>
-      <c r="G1669" t="inlineStr"/>
+      <c r="G1669" t="n">
+        <v>68725678.249</v>
+      </c>
       <c r="H1669" t="inlineStr"/>
     </row>
     <row r="1670">
       <c r="A1670" s="1" t="n">
         <v>46300</v>
       </c>
-      <c r="B1670" t="inlineStr"/>
-      <c r="C1670" t="inlineStr"/>
+      <c r="B1670" t="n">
+        <v>48798</v>
+      </c>
+      <c r="C1670" t="n">
+        <v>46422891</v>
+      </c>
       <c r="D1670" t="n">
         <v>1540.24</v>
       </c>
-      <c r="E1670" t="inlineStr"/>
+      <c r="E1670" t="n">
+        <v>21.625</v>
+      </c>
       <c r="F1670" t="inlineStr"/>
-      <c r="G1670" t="inlineStr"/>
+      <c r="G1670" t="n">
+        <v>67850570.987</v>
+      </c>
       <c r="H1670" t="inlineStr"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1671" t="n">
+        <v>49125</v>
+      </c>
+      <c r="C1671" t="n">
+        <v>46779479</v>
+      </c>
+      <c r="D1671" t="n">
+        <v>1541.41</v>
+      </c>
+      <c r="E1671" t="n">
+        <v>22.8125</v>
+      </c>
+      <c r="F1671" t="inlineStr"/>
+      <c r="G1671" t="n">
+        <v>68107404.786</v>
+      </c>
+      <c r="H1671" t="inlineStr"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1672" t="n">
+        <v>49133</v>
+      </c>
+      <c r="C1672" t="n">
+        <v>46710066</v>
+      </c>
+      <c r="D1672" t="n">
+        <v>1543.08</v>
+      </c>
+      <c r="E1672" t="n">
+        <v>21.4375</v>
+      </c>
+      <c r="F1672" t="inlineStr"/>
+      <c r="G1672" t="inlineStr"/>
+      <c r="H1672" t="inlineStr"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1673" t="inlineStr"/>
+      <c r="C1673" t="inlineStr"/>
+      <c r="D1673" t="n">
+        <v>1539.3</v>
+      </c>
+      <c r="E1673" t="n">
+        <v>22.375</v>
+      </c>
+      <c r="F1673" t="inlineStr"/>
+      <c r="G1673" t="inlineStr"/>
+      <c r="H1673" t="inlineStr"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1674" t="inlineStr"/>
+      <c r="C1674" t="inlineStr"/>
+      <c r="D1674" t="n">
+        <v>1537.18</v>
+      </c>
+      <c r="E1674" t="inlineStr"/>
+      <c r="F1674" t="inlineStr"/>
+      <c r="G1674" t="inlineStr"/>
+      <c r="H1674" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
